--- a/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1648,11 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1734,11 +1834,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">

--- a/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -1383,7 +1383,7 @@
       </c>
       <c r="AA7" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB7" s="6" t="n"/>
@@ -1460,14 +1460,14 @@
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
       <c r="O8" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R8" s="6" t="n"/>
@@ -1477,14 +1477,14 @@
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
       <c r="X8" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AA8" s="6" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AA9" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB9" s="6" t="n"/>
@@ -1672,14 +1672,14 @@
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R10" s="6" t="n"/>
@@ -1689,14 +1689,14 @@
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
       <c r="X10" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="Y10" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AA10" s="6" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AA11" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB11" s="6" t="n"/>
@@ -1884,14 +1884,14 @@
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
       <c r="O12" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R12" s="6" t="n"/>

--- a/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -1940,32 +1940,88 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2243A02</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2243002</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
-      <c r="AA13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="6" t="n"/>
@@ -1990,32 +2046,88 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2243A02</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2243002</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
-      <c r="AA14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AA14" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
       <c r="AD14" s="6" t="n"/>
@@ -2040,32 +2152,88 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2243A02</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2243002</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
-      <c r="AA15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AA15" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="6" t="n"/>
@@ -2090,32 +2258,88 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2243A02</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2243002</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
-      <c r="AA16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AA16" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
       <c r="AD16" s="6" t="n"/>
@@ -2140,32 +2364,88 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2243A02</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2243002</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
-      <c r="AA17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
       <c r="AD17" s="6" t="n"/>
@@ -2190,32 +2470,88 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2243A02</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2243002</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="O18" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
-      <c r="AA18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA18" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
       <c r="AD18" s="6" t="n"/>

--- a/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00026_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1339,7 +1339,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>27</v>
       </c>
@@ -1445,7 +1449,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>45</v>
       </c>
@@ -1518,22 +1526,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2243A01</t>
+          <t>2243A02</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2243001</t>
+          <t>2243002</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1551,7 +1559,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
         <v>24</v>
       </c>
@@ -1624,22 +1636,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2243A01</t>
+          <t>2243A02</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2243001</t>
+          <t>2243002</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1657,7 +1669,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
         <v>36</v>
       </c>
@@ -1728,88 +1744,32 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA11" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
+      <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
       <c r="AD11" s="6" t="n"/>
@@ -1834,88 +1794,32 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
+      <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
       <c r="AD12" s="6" t="n"/>
@@ -1940,88 +1844,32 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y13" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z13" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="6" t="n"/>
+      <c r="Z13" s="6" t="n"/>
+      <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="6" t="n"/>
@@ -2046,88 +1894,32 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y14" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z14" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="6" t="n"/>
+      <c r="Z14" s="6" t="n"/>
+      <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
       <c r="AD14" s="6" t="n"/>
@@ -2152,88 +1944,32 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="n"/>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y15" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z15" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="6" t="n"/>
@@ -2258,88 +1994,32 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y16" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z16" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
+      <c r="Z16" s="6" t="n"/>
+      <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
       <c r="AD16" s="6" t="n"/>
@@ -2364,88 +2044,32 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
+      <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
       <c r="AD17" s="6" t="n"/>
@@ -2470,88 +2094,32 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
+      <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
       <c r="AD18" s="6" t="n"/>
